--- a/EVSales.xlsx
+++ b/EVSales.xlsx
@@ -9,14 +9,13 @@
   </bookViews>
   <sheets>
     <sheet name="SalesData" sheetId="5" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId2"/>
-    <sheet name="Sales (Brand)" sheetId="4" r:id="rId3"/>
-    <sheet name="Ranking" sheetId="7" r:id="rId4"/>
-    <sheet name="Main_" sheetId="1" r:id="rId5"/>
+    <sheet name="Sales (Brand)" sheetId="4" r:id="rId2"/>
+    <sheet name="Ranking" sheetId="7" r:id="rId3"/>
+    <sheet name="Main_" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -57,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3897" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3897" uniqueCount="525">
   <si>
     <t>record_id</t>
   </si>
@@ -1954,11 +1953,53 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1975,57 +2016,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="39">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2415,6 +2411,9 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6120,8 +6119,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7054317" y="5032737"/>
-          <a:ext cx="15163800" cy="3534786"/>
+          <a:off x="7051061" y="5050322"/>
+          <a:ext cx="15127327" cy="3546509"/>
           <a:chOff x="6831950" y="5298739"/>
           <a:chExt cx="13096723" cy="3420905"/>
         </a:xfrm>
@@ -14366,7 +14365,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25715D0A-3E81-C34C-82D6-C3E46B3EA84B}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25715D0A-3E81-C34C-82D6-C3E46B3EA84B}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A2:D421" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="16">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -16973,7 +16972,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7A5E1302-6ACF-4E40-994D-5817EC309613}" name="Table35" displayName="Table35" ref="H16:I20" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7A5E1302-6ACF-4E40-994D-5817EC309613}" name="Table35" displayName="Table35" ref="H16:I20" totalsRowShown="0" headerRowDxfId="24">
   <autoFilter ref="H16:I20" xr:uid="{7A5E1302-6ACF-4E40-994D-5817EC309613}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{CD8122E3-FA05-C149-BC7C-9D98015606C0}" name="Regional Sales "/>
@@ -16999,32 +16998,32 @@
   <autoFilter ref="J10:K16" xr:uid="{DF348AA7-24BC-AD40-95CA-3ABB23A6A92D}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{EE1F2306-4101-564E-A7B2-2ADB5743DA00}" name="PercentileFunction"/>
-    <tableColumn id="2" xr3:uid="{9345E067-A447-474C-A7E3-ED7F0B414D65}" name="Array,Percentile" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{9345E067-A447-474C-A7E3-ED7F0B414D65}" name="Array,Percentile" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C423A507-14B9-4040-825B-E3C9DA9D6F7D}" name="Table2" displayName="Table2" ref="A1:P419" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C423A507-14B9-4040-825B-E3C9DA9D6F7D}" name="Table2" displayName="Table2" ref="A1:P419" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:P419" xr:uid="{C423A507-14B9-4040-825B-E3C9DA9D6F7D}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{F6B419AA-8E1C-DE4C-8032-28795C5D8805}" name="record_id" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{9386DEB1-C1C5-104A-937F-E40DC9411A1D}" name="country" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{72581B34-256C-6A46-B4A6-DDE39F754ED8}" name="region" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{763FF9C6-5B3D-5345-9923-8C0A43DA2336}" name="ev_brand" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{A19DD24E-F2A5-134B-AA1A-841B3A138D6A}" name="vehicle_type" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{40E01E24-CFE7-1D4C-ACE0-BBECA47D5359}" name="ev_sales_units" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{9220EAC7-64B5-0A48-995A-7FCB51D9018F}" name="battery_capacity_kwh" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{DBC4751D-DB0F-3544-97F8-45326CB57E78}" name="vehicle_range_km" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{5996C551-C748-8D45-BB3D-0A0059B3D842}" name="charging_time_hours" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{72B80493-9230-2643-AF13-22B0EC905D5F}" name="charging_stations" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{16902F1B-AC6D-4748-8630-70D896C6DE1D}" name="avg_ev_price_usd" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{32D26617-B3CA-6C42-91B0-EE5994CA02D1}" name="energy_consumption_kwh" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{689EEDD0-F66F-FC4C-8D55-07814FD202BF}" name="govt_incentives" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{A39CB04B-A759-A440-A007-E0E27335070C}" name="market_adoption_rate" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{CB5765A9-E221-A347-B1C8-868511A2F9F0}" name="co2_reduction_mt" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{CDDF72B0-49C7-8447-8B23-1EF5FD00B4F3}" name="year" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{F6B419AA-8E1C-DE4C-8032-28795C5D8805}" name="record_id" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{9386DEB1-C1C5-104A-937F-E40DC9411A1D}" name="country" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{72581B34-256C-6A46-B4A6-DDE39F754ED8}" name="region" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{763FF9C6-5B3D-5345-9923-8C0A43DA2336}" name="ev_brand" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{A19DD24E-F2A5-134B-AA1A-841B3A138D6A}" name="vehicle_type" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{40E01E24-CFE7-1D4C-ACE0-BBECA47D5359}" name="ev_sales_units" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{9220EAC7-64B5-0A48-995A-7FCB51D9018F}" name="battery_capacity_kwh" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{DBC4751D-DB0F-3544-97F8-45326CB57E78}" name="vehicle_range_km" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{5996C551-C748-8D45-BB3D-0A0059B3D842}" name="charging_time_hours" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{72B80493-9230-2643-AF13-22B0EC905D5F}" name="charging_stations" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{16902F1B-AC6D-4748-8630-70D896C6DE1D}" name="avg_ev_price_usd" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{32D26617-B3CA-6C42-91B0-EE5994CA02D1}" name="energy_consumption_kwh" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{689EEDD0-F66F-FC4C-8D55-07814FD202BF}" name="govt_incentives" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{A39CB04B-A759-A440-A007-E0E27335070C}" name="market_adoption_rate" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{CB5765A9-E221-A347-B1C8-868511A2F9F0}" name="co2_reduction_mt" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{CDDF72B0-49C7-8447-8B23-1EF5FD00B4F3}" name="year" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium24" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17382,13 +17381,13 @@
       <c r="D2" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="31" t="s">
         <v>469</v>
       </c>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -17597,11 +17596,11 @@
       <c r="D9" s="3">
         <v>648873</v>
       </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -18252,19 +18251,19 @@
       <c r="D45" s="3">
         <v>21380</v>
       </c>
-      <c r="H45" s="25" t="s">
+      <c r="H45" s="18" t="s">
         <v>508</v>
       </c>
-      <c r="I45" s="26" t="s">
+      <c r="I45" s="19" t="s">
         <v>507</v>
       </c>
-      <c r="J45" s="26" t="s">
+      <c r="J45" s="19" t="s">
         <v>513</v>
       </c>
       <c r="K45" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="L45" s="24" t="s">
+      <c r="L45" s="17" t="s">
         <v>514</v>
       </c>
     </row>
@@ -18281,12 +18280,12 @@
       <c r="D46" s="3">
         <v>688173</v>
       </c>
-      <c r="H46" s="31" t="s">
+      <c r="H46" s="33" t="s">
         <v>517</v>
       </c>
-      <c r="I46" s="32"/>
-      <c r="J46" s="33"/>
-      <c r="L46" s="24" t="s">
+      <c r="I46" s="34"/>
+      <c r="J46" s="35"/>
+      <c r="L46" s="17" t="s">
         <v>520</v>
       </c>
     </row>
@@ -18303,16 +18302,16 @@
       <c r="D47" s="3">
         <v>664493</v>
       </c>
-      <c r="H47" s="34" t="s">
+      <c r="H47" s="23" t="s">
         <v>510</v>
       </c>
-      <c r="I47" s="28" t="s">
+      <c r="I47" s="21" t="s">
         <v>511</v>
       </c>
-      <c r="J47" s="35" t="s">
+      <c r="J47" s="24" t="s">
         <v>512</v>
       </c>
-      <c r="L47" s="24" t="s">
+      <c r="L47" s="17" t="s">
         <v>521</v>
       </c>
     </row>
@@ -18329,13 +18328,13 @@
       <c r="D48" s="3">
         <v>876218</v>
       </c>
-      <c r="H48" s="36" t="s">
+      <c r="H48" s="25" t="s">
         <v>503</v>
       </c>
-      <c r="I48" s="29" t="s">
+      <c r="I48" s="22" t="s">
         <v>512</v>
       </c>
-      <c r="J48" s="37" t="s">
+      <c r="J48" s="26" t="s">
         <v>512</v>
       </c>
     </row>
@@ -18352,13 +18351,13 @@
       <c r="D49" s="3">
         <v>622503</v>
       </c>
-      <c r="H49" s="34" t="s">
+      <c r="H49" s="23" t="s">
         <v>504</v>
       </c>
-      <c r="I49" s="29" t="s">
+      <c r="I49" s="22" t="s">
         <v>512</v>
       </c>
-      <c r="J49" s="37" t="s">
+      <c r="J49" s="26" t="s">
         <v>512</v>
       </c>
     </row>
@@ -18375,15 +18374,15 @@
       <c r="D50" s="3">
         <v>96400</v>
       </c>
-      <c r="H50" s="38" t="s">
+      <c r="H50" s="36" t="s">
         <v>518</v>
       </c>
-      <c r="I50" s="30"/>
-      <c r="J50" s="39"/>
-      <c r="K50" s="27" t="s">
+      <c r="I50" s="37"/>
+      <c r="J50" s="38"/>
+      <c r="K50" s="20" t="s">
         <v>522</v>
       </c>
-      <c r="L50" s="43" t="s">
+      <c r="L50" s="30" t="s">
         <v>523</v>
       </c>
     </row>
@@ -18400,16 +18399,16 @@
       <c r="D51" s="3">
         <v>194579</v>
       </c>
-      <c r="H51" s="36" t="s">
+      <c r="H51" s="25" t="s">
         <v>505</v>
       </c>
-      <c r="I51" s="29" t="s">
+      <c r="I51" s="22" t="s">
         <v>512</v>
       </c>
-      <c r="J51" s="37" t="s">
+      <c r="J51" s="26" t="s">
         <v>512</v>
       </c>
-      <c r="L51" s="43" t="s">
+      <c r="L51" s="30" t="s">
         <v>524</v>
       </c>
     </row>
@@ -18426,13 +18425,13 @@
       <c r="D52" s="3">
         <v>42529</v>
       </c>
-      <c r="H52" s="40" t="s">
+      <c r="H52" s="27" t="s">
         <v>506</v>
       </c>
-      <c r="I52" s="41" t="s">
+      <c r="I52" s="28" t="s">
         <v>512</v>
       </c>
-      <c r="J52" s="42" t="s">
+      <c r="J52" s="29" t="s">
         <v>512</v>
       </c>
     </row>
@@ -23629,15 +23628,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5751D76-A2DE-DB40-A66A-1F223D4A9487}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C35D98-CE1A-E44B-9BB1-5E15732D0E3A}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -23767,7 +23757,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A07FAFF3-A34E-EB46-B222-1A024886C473}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -23912,10 +23902,10 @@
       <c r="I9" s="15" t="s">
         <v>502</v>
       </c>
-      <c r="J9" s="23" t="s">
+      <c r="J9" s="43" t="s">
         <v>494</v>
       </c>
-      <c r="K9" s="23"/>
+      <c r="K9" s="43"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
@@ -23928,13 +23918,13 @@
         <v>714686</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="39" t="s">
         <v>490</v>
       </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="21"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="41"/>
       <c r="J10" t="s">
         <v>494</v>
       </c>
@@ -23959,10 +23949,10 @@
       <c r="F11" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="42" t="s">
         <v>497</v>
       </c>
-      <c r="H11" s="22"/>
+      <c r="H11" s="42"/>
       <c r="I11" s="13" t="s">
         <v>495</v>
       </c>
@@ -24101,25 +24091,25 @@
   </mergeCells>
   <phoneticPr fontId="5" alignment="center"/>
   <conditionalFormatting sqref="J11:K11">
-    <cfRule type="top10" dxfId="5" priority="6" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="4" priority="6" percent="1" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>0.25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24130,7 +24120,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64988B4C-39B3-A345-92C5-43B96C07B3BC}">
   <dimension ref="A1:P419"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
